--- a/src/transactions.xlsx
+++ b/src/transactions.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:I147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,91 +428,5920 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>currency_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>currency_code</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2130098</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1500.5</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>43989.46638888889</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30731</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>withdrawal</t>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Visa 5749750597771353</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>American Express 9106381490184499</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4653427</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3200</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>44108.50859953704</v>
+      </c>
+      <c r="D3" t="n">
+        <v>34072</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>deposit</t>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Discover 9058011549803523</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Mastercard 5266726031439012</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>5371445</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>-800.75</v>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>45218.16079861111</v>
+      </c>
+      <c r="D4" t="n">
+        <v>19556</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Discover 2269057629158313</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Discover 1467530652300402</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5368178</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>44019.58126157407</v>
+      </c>
+      <c r="D5" t="n">
+        <v>22557</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Mastercard 4225154400758745</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Mastercard 0556460753444710</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1068715</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>45141.66709490741</v>
+      </c>
+      <c r="D6" t="n">
+        <v>18891</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Счет 04362233061130879079</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2051401</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>44940.58314814815</v>
+      </c>
+      <c r="D7" t="n">
+        <v>21616</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Franc</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>XAF</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Discover 8023806415405011</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Discover 4330675064880873</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2377317</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>45152.41575231482</v>
+      </c>
+      <c r="D8" t="n">
+        <v>23305</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Koruna</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Счет 60476196595963796362</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1781876</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>44977.46435185185</v>
+      </c>
+      <c r="D9" t="n">
+        <v>24586</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Franc</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>XAF</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>American Express 4188660988695878</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>American Express 4670165143133955</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>632926</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>44527.03204861111</v>
+      </c>
+      <c r="D10" t="n">
+        <v>29553</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>American Express 6477627838877562</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Счет 88381741644903346269</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5055836</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>44656.14523148148</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24796</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Zloty</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Mastercard 3588035503290783</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Счет 44168961306050363869</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>282352</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>44191.40208333333</v>
+      </c>
+      <c r="D12" t="n">
+        <v>32566</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Счет 87117715624747483097</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3463793</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>43886.3090162037</v>
+      </c>
+      <c r="D13" t="n">
+        <v>17655</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ruble</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>transfer</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Mastercard 4597611385572324</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Visa 0264849140954307</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5008516</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>45107.18858796296</v>
+      </c>
+      <c r="D14" t="n">
+        <v>19988</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Baht</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Discover 0631296518388969</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Mastercard 6497034908492124</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1453305</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>43989.08885416666</v>
+      </c>
+      <c r="D15" t="n">
+        <v>12234</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ruble</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Visa 6644696207526766</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Mastercard 8548964838326541</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5434073</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>44120.02321759259</v>
+      </c>
+      <c r="D16" t="n">
+        <v>33634</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Discover 6079985810069539</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>American Express 4187003076609282</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5379915</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>45158.12024305556</v>
+      </c>
+      <c r="D17" t="n">
+        <v>24850</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Yen</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Счет 36811391490389049691</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>368297</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>44671.07193287037</v>
+      </c>
+      <c r="D18" t="n">
+        <v>12362</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sol</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Счет 73197209028710375773</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>744365</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>44684.21193287037</v>
+      </c>
+      <c r="D19" t="n">
+        <v>22652</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Dollar</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Discover 8093960331401116</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Mastercard 1224722159463490</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1221992</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>44246.55940972222</v>
+      </c>
+      <c r="D20" t="n">
+        <v>12918</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ruble</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Mastercard 9775497812609116</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Discover 5944506116473459</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3518973</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>45210.04398148148</v>
+      </c>
+      <c r="D21" t="n">
+        <v>19653</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Visa 0383646897791685</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>American Express 9980918985573635</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3513019</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>44806.24712962963</v>
+      </c>
+      <c r="D22" t="n">
+        <v>13127</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Discover 3114252861244492</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Visa 4627389712448189</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1379139</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>44705.86199074074</v>
+      </c>
+      <c r="D23" t="n">
+        <v>14160</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Manat</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>AZN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Discover 9659662475890450</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Discover 1864760256062832</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2611948</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>44600.71950231482</v>
+      </c>
+      <c r="D24" t="n">
+        <v>15911</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ruble</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Discover 6348321385395461</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Mastercard 7325946652944710</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4924104</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>44354.72460648148</v>
+      </c>
+      <c r="D25" t="n">
+        <v>13036</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>MGA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Mastercard 9984189726356135</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>American Express 9496683068632548</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3456154</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>44594.49076388889</v>
+      </c>
+      <c r="D26" t="n">
+        <v>16193</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Visa 8600999617172909</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Visa 2844866498722428</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>599027</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>44613.12265046296</v>
+      </c>
+      <c r="D27" t="n">
+        <v>12373</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>American Express 6311535048493715</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Discover 6103555688511371</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3327991</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>43832.62287037037</v>
+      </c>
+      <c r="D28" t="n">
+        <v>21565</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Tenge</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Visa 6101438539947726</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Mastercard 1093643052935424</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>4768701</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>44770.29969907407</v>
+      </c>
+      <c r="D29" t="n">
+        <v>14922</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Discover 9845271582621310</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Discover 2528293109343153</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2850514</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>44193.74528935185</v>
+      </c>
+      <c r="D30" t="n">
+        <v>23686</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Lek</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Discover 9576458861815708</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Mastercard 4321975182864595</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1279142</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>43873.56762731481</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16376</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Yen</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Mastercard 5444471272260826</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Visa 9213489075974563</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2300960</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>43961.88818287037</v>
+      </c>
+      <c r="D32" t="n">
+        <v>21170</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>American Express 2077167756122624</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Счет 12692107571051189313</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3015231</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>44574.13541666666</v>
+      </c>
+      <c r="D33" t="n">
+        <v>21470</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Mastercard 9800302102501629</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Mastercard 2405382947502377</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1380530</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>45068.53460648148</v>
+      </c>
+      <c r="D34" t="n">
+        <v>32118</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Dong</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Discover 1625204231900607</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Mastercard 6547698108887955</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3415187</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>44844.04048611111</v>
+      </c>
+      <c r="D35" t="n">
+        <v>25180</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>American Express 0358075953034789</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Visa 7020384213026064</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>4026887</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>44518.30319444444</v>
+      </c>
+      <c r="D36" t="n">
+        <v>34138</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Discover 1747353075279525</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Visa 3125438085014296</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>879954</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>44612.02410879629</v>
+      </c>
+      <c r="D37" t="n">
+        <v>19037</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>American Express 7505798122789172</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>American Express 4033942449270190</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2352308</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>44540.1234837963</v>
+      </c>
+      <c r="D38" t="n">
+        <v>11358</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Lempira</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>HNL</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Mastercard 9035732695110352</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Visa 8440267076775146</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4754778</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>45007.80353009259</v>
+      </c>
+      <c r="D39" t="n">
+        <v>14992</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Kyat</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>MMK</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Discover 9055259074920445</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>American Express 3629785004484612</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1358349</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>44109.43885416666</v>
+      </c>
+      <c r="D40" t="n">
+        <v>31503</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Ruble</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Счет 69086868315648596195</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>379155</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>44292.85083333333</v>
+      </c>
+      <c r="D41" t="n">
+        <v>23765</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ruble</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>BYR</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Счет 47740967047235244813</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1718927</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>43860.00405092593</v>
+      </c>
+      <c r="D42" t="n">
+        <v>11284</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Счет 58661644025578523199</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2367328</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>44802.68231481482</v>
+      </c>
+      <c r="D43" t="n">
+        <v>27012</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Franc</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>XOF</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Discover 1781865926439519</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>American Express 7807738435996717</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3896277</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>44932.42857638889</v>
+      </c>
+      <c r="D44" t="n">
+        <v>12077</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Счет 38786697703780679258</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4547801</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>44947.99929398148</v>
+      </c>
+      <c r="D45" t="n">
+        <v>14109</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Счет 37292228167431639458</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2927678</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>43941.36869212963</v>
+      </c>
+      <c r="D46" t="n">
+        <v>22584</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Krona</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Visa 5273150871379598</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Visa 2228394034527340</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2460621</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>44163.62784722223</v>
+      </c>
+      <c r="D47" t="n">
+        <v>18158</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Счет 96408418161748634691</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1100171</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>44210.29738425926</v>
+      </c>
+      <c r="D48" t="n">
+        <v>11683</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Leu</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>MDL</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Счет 08116016835671035018</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4935914</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>45209.10013888889</v>
+      </c>
+      <c r="D49" t="n">
+        <v>21686</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Zloty</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>American Express 6113480057863136</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Discover 4775142254527406</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4136534</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>44988.81375</v>
+      </c>
+      <c r="D50" t="n">
+        <v>21909</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Dollar</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Mastercard 4534142823002219</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Счет 26030281604290741032</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4333005</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>43867.48361111111</v>
+      </c>
+      <c r="D51" t="n">
+        <v>12480</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Ruble</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Mastercard 7673263953329337</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Discover 6961587092605561</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>3530319</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>44600.78423611111</v>
+      </c>
+      <c r="D52" t="n">
+        <v>11294</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Pound</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SYP</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Счет 64339097692172543801</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Счет 65515023539147659794</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Перевод со счета на счет</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4585117</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>44864.05114583333</v>
+      </c>
+      <c r="D53" t="n">
+        <v>31183</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Shekel</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>American Express 1645890173600671</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>American Express 4738095110228336</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2236163</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>45106.85690972222</v>
+      </c>
+      <c r="D54" t="n">
+        <v>19612</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Счет 40742441133364006255</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Счет 52562367063354770261</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Перевод со счета на счет</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>5245387</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>45149.28736111111</v>
+      </c>
+      <c r="D55" t="n">
+        <v>25234</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>American Express 8621646228906535</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>American Express 8098137039932677</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>481674</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>45104.47019675926</v>
+      </c>
+      <c r="D56" t="n">
+        <v>24192</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Счет 30690764917065605785</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>5453219</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>44008.81377314815</v>
+      </c>
+      <c r="D57" t="n">
+        <v>34289</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Koruna</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Счет 23862786914703615175</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2961341</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>44900.91804398148</v>
+      </c>
+      <c r="D58" t="n">
+        <v>19724</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Visa 5505312713585497</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Счет 63298657753084851664</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4981054</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>44735.2599537037</v>
+      </c>
+      <c r="D59" t="n">
+        <v>30316</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Baht</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Счет 90489082675296745022</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>145602</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>44831.81436342592</v>
+      </c>
+      <c r="D60" t="n">
+        <v>20423</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Dollar</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Счет 96420288541936966744</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>470092</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>44168.62060185185</v>
+      </c>
+      <c r="D61" t="n">
+        <v>30922</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Hryvnia</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Счет 73554102589353530426</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3243213</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>44046.53327546296</v>
+      </c>
+      <c r="D62" t="n">
+        <v>18212</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Mastercard 6840667987524201</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4877288</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>45007.87980324074</v>
+      </c>
+      <c r="D63" t="n">
+        <v>32771</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Hryvnia</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Discover 3175955318657678</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>American Express 9365944599565412</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>5161584</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>44206.49123842592</v>
+      </c>
+      <c r="D64" t="n">
+        <v>21117</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Baht</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Visa 7161243147790334</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Счет 76355617883095566183</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2848273</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>44939.85696759259</v>
+      </c>
+      <c r="D65" t="n">
+        <v>18871</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Tugrik</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>MNT</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Счет 13106498680479579714</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3146089</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>44994.32703703704</v>
+      </c>
+      <c r="D66" t="n">
+        <v>30095</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>NIO</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Mastercard 1871929909720556</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Mastercard 4747357637092907</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>516388</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>44157.70619212963</v>
+      </c>
+      <c r="D67" t="n">
+        <v>27921</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Dinar</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>JOD</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Mastercard 7201033785622479</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Счет 28268105792239263134</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1220204</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>44603.06378472222</v>
+      </c>
+      <c r="D68" t="n">
+        <v>11686</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Dollar</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Mastercard 4605227118045463</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>American Express 5253972174427993</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3080997</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>43879.61677083333</v>
+      </c>
+      <c r="D69" t="n">
+        <v>31240</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Baht</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Счет 49075406587701019462</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>552769</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>43832.06026620371</v>
+      </c>
+      <c r="D70" t="n">
+        <v>26325</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Krona</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Discover 5367334867736788</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Visa 3673180759636903</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>3394763</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>45117.40854166666</v>
+      </c>
+      <c r="D71" t="n">
+        <v>31406</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Yen</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Discover 0769625831234066</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Счет 89698444160396708996</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>671684</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>44725.11576388889</v>
+      </c>
+      <c r="D72" t="n">
+        <v>27114</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Dollar</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Discover 9737807541197254</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Discover 0342605798844488</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4174847</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>44138.6059375</v>
+      </c>
+      <c r="D73" t="n">
+        <v>15196</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Dong</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Mastercard 2491943868249693</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Discover 7077798977965820</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>3684712</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>44784.41809027778</v>
+      </c>
+      <c r="D74" t="n">
+        <v>13555</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>American Express 3187719566240886</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>American Express 4694809375452950</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3724901</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>44345.82913194445</v>
+      </c>
+      <c r="D75" t="n">
+        <v>33410</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>American Express 0208810830776920</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Mastercard 4495966967290894</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1999804</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>45227.47049768519</v>
+      </c>
+      <c r="D76" t="n">
+        <v>34455</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Hryvnia</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Счет 42109207415591580635</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Счет 74058089109726743250</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Перевод со счета на счет</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1976993</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>44476.80891203704</v>
+      </c>
+      <c r="D77" t="n">
+        <v>14950</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Pound</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>SYP</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Discover 5138829471442482</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Счет 86520143612658802382</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1560456</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>45115.65166666666</v>
+      </c>
+      <c r="D78" t="n">
+        <v>15726</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Visa 1576854615043358</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Счет 55484214540765770320</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2432689</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>44549.33715277778</v>
+      </c>
+      <c r="D79" t="n">
+        <v>16687</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Discover 0100855364826755</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Mastercard 8643424644765562</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4315096</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>44282.80520833333</v>
+      </c>
+      <c r="D80" t="n">
+        <v>16271</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Zloty</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>American Express 3568441571958482</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Discover 0688707149480292</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>3932469</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>44621.78141203704</v>
+      </c>
+      <c r="D81" t="n">
+        <v>21678</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Discover 0803276764821082</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Mastercard 6602596422358257</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>5170766</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>44937.77875</v>
+      </c>
+      <c r="D82" t="n">
+        <v>15534</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Quetzal</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>GTQ</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Счет 91269211633331489581</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Счет 83962090923263746792</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Перевод со счета на счет</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>3081948</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>44503.39019675926</v>
+      </c>
+      <c r="D83" t="n">
+        <v>26241</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Visa 6774409271534698</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Discover 6125995337388389</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>3458538</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>44496.84827546297</v>
+      </c>
+      <c r="D84" t="n">
+        <v>25247</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Mastercard 8198255172011752</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>American Express 1521610110014693</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>5184881</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>45175.09075231481</v>
+      </c>
+      <c r="D85" t="n">
+        <v>26661</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Visa 9854254255741256</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Visa 1574192240031041</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2327667</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>44758.71872685185</v>
+      </c>
+      <c r="D86" t="n">
+        <v>31550</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>American Express 3307640951904332</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>American Express 8561768757933328</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1595672</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>44211.27791666667</v>
+      </c>
+      <c r="D87" t="n">
+        <v>27346</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Guilder</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ANG</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Discover 3800548259118301</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>American Express 3857603686856041</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4492444</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>44817.11194444444</v>
+      </c>
+      <c r="D88" t="n">
+        <v>13086</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Dollar</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Счет 07318089075038053901</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Счет 05172516288862953128</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Перевод со счета на счет</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>590436</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>44954.2778125</v>
+      </c>
+      <c r="D89" t="n">
+        <v>25193</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Счет 46780854004272996593</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>5416009</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>44763.74369212963</v>
+      </c>
+      <c r="D90" t="n">
+        <v>14827</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>American Express 3294381045631862</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Счет 82941857947209957540</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>3386429</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>44324.36054398148</v>
+      </c>
+      <c r="D91" t="n">
+        <v>16216</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Discover 1256970763079173</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Счет 57605402872278121538</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2151382</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>45023.0697337963</v>
+      </c>
+      <c r="D92" t="n">
+        <v>19607</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Baht</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Discover 1869571162526318</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>American Express 8377763578542307</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>3636529</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>44309.77895833334</v>
+      </c>
+      <c r="D93" t="n">
+        <v>17449</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Naira</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>NGN</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>American Express 2245008812200631</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>American Express 5496713030087267</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4668685</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>44644.36460648148</v>
+      </c>
+      <c r="D94" t="n">
+        <v>34310</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Mastercard 4272685591982566</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Discover 1114381807822930</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1681932</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>44192.46844907408</v>
+      </c>
+      <c r="D95" t="n">
+        <v>11863</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Som</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Discover 4249648000496538</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Discover 4478419247437211</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1274896</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>44850.47024305556</v>
+      </c>
+      <c r="D96" t="n">
+        <v>19839</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Discover 5514977218468856</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Mastercard 6902754210775301</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>846157</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>43899.1303125</v>
+      </c>
+      <c r="D97" t="n">
+        <v>31775</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Mastercard 8838784203105980</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Visa 9604746164148154</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>3701103</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>44069.14635416667</v>
+      </c>
+      <c r="D98" t="n">
+        <v>27435</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Mastercard 9762476852200502</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Visa 1032017250021833</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1986491</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>44281.11376157407</v>
+      </c>
+      <c r="D99" t="n">
+        <v>27106</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Ruble</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>BYR</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Счет 49835166076184371589</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>5229572</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>44912.67439814815</v>
+      </c>
+      <c r="D100" t="n">
+        <v>18347</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Mastercard 7491706274351135</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Discover 7569170634837533</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2812198</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>43984.14090277778</v>
+      </c>
+      <c r="D101" t="n">
+        <v>31822</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Discover 0632158083785792</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>American Express 0532003528871708</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>115625</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>44969.93266203703</v>
+      </c>
+      <c r="D102" t="n">
+        <v>17130</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Mastercard 0149845709452157</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Счет 77767569336476668437</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>90523</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>44084.64658564814</v>
+      </c>
+      <c r="D103" t="n">
+        <v>32773</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Discover 2856040699058042</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Visa 6194726895133398</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1428564</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>44972.73545138889</v>
+      </c>
+      <c r="D104" t="n">
+        <v>14411</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Franc</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>XAF</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Visa 6741609188063628</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Discover 0163518015691189</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2129219</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>45143.78532407407</v>
+      </c>
+      <c r="D105" t="n">
+        <v>29187</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Visa 1543704869759627</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Mastercard 7023874989167897</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>601829</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>45191.21229166666</v>
+      </c>
+      <c r="D106" t="n">
+        <v>31130</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Discover 0930552143364376</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>American Express 5163534531737636</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>4266692</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>44861.61912037037</v>
+      </c>
+      <c r="D107" t="n">
+        <v>11180</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Mastercard 4407294553976321</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Счет 35208387182106672186</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>814363</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>43859.29630787037</v>
+      </c>
+      <c r="D108" t="n">
+        <v>29906</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>American Express 0248447631215432</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>American Express 3856315470030794</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>3167437</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>44682.10469907407</v>
+      </c>
+      <c r="D109" t="n">
+        <v>25367</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Leu</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>MDL</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Discover 6290853444919537</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>American Express 3907611664671296</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2258909</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>45082.0233912037</v>
+      </c>
+      <c r="D110" t="n">
+        <v>27030</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Rand</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>ZAR</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Счет 95883985429884067440</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Счет 98017798502227556609</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Перевод со счета на счет</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2449358</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>45006.64050925926</v>
+      </c>
+      <c r="D111" t="n">
+        <v>28671</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Hryvnia</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Счет 09503816595143782708</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Счет 88842829646860865403</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Перевод со счета на счет</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1463688</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>44538.59173611111</v>
+      </c>
+      <c r="D112" t="n">
+        <v>18989</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>American Express 7431983574131577</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Счет 08858102338416536409</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>3821850</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>45148.67325231482</v>
+      </c>
+      <c r="D113" t="n">
+        <v>23816</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Счет 82229490370109855587</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1786943</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>44841.11903935186</v>
+      </c>
+      <c r="D114" t="n">
+        <v>29551</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Kwacha</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ZMW</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Discover 1321143733747621</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>American Express 8378555854465389</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2467622</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>45138.67976851852</v>
+      </c>
+      <c r="D115" t="n">
+        <v>15845</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>American Express 3407907218075851</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Discover 3920809225480647</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>3205257</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>44662.02134259259</v>
+      </c>
+      <c r="D116" t="n">
+        <v>11280</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Ruble</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Mastercard 5612504218607911</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Счет 96692813169753520384</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1932532</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>43880.01195601852</v>
+      </c>
+      <c r="D117" t="n">
+        <v>25246</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Forint</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>HUF</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Discover 6177546839517597</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>American Express 9695664158183113</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>4541322</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>44686.24666666667</v>
+      </c>
+      <c r="D118" t="n">
+        <v>11483</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Franc</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>XOF</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>American Express 0478677534311566</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>American Express 8772778718443997</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>3400976</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>44577.39273148148</v>
+      </c>
+      <c r="D119" t="n">
+        <v>16702</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Pound</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>SYP</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Visa 2627051318570658</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Счет 67891866687752369595</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>4565275</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>44367.46054398148</v>
+      </c>
+      <c r="D120" t="n">
+        <v>19321</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Ruble</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>American Express 2932525563014117</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>American Express 3633642385468444</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>2697434</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>45221.42153935185</v>
+      </c>
+      <c r="D121" t="n">
+        <v>19405</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Discover 3984228285377185</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Discover 2678102579384092</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>2455963</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>45010.43490740741</v>
+      </c>
+      <c r="D122" t="n">
+        <v>31704</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Ringgit</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Счет 47700019920719928388</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>2835186</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>44983.68815972222</v>
+      </c>
+      <c r="D123" t="n">
+        <v>32137</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Dinar</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>JOD</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Счет 08293202872152338638</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>3509357</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>44655.08723379629</v>
+      </c>
+      <c r="D124" t="n">
+        <v>25427</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Sol</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Visa 0317106056412201</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Счет 31080002409662710330</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>5457678</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>45234.44414351852</v>
+      </c>
+      <c r="D125" t="n">
+        <v>22951</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Mastercard 6219443780959412</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Visa 4786131684105875</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>3188844</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>45153.85173611111</v>
+      </c>
+      <c r="D126" t="n">
+        <v>23993</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Visa 7320406476027149</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>American Express 4821240054296686</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>3048608</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>44199.11275462963</v>
+      </c>
+      <c r="D127" t="n">
+        <v>25207</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Mastercard 5983030475609063</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Discover 8166276555625267</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>5270713</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>43996.29068287037</v>
+      </c>
+      <c r="D128" t="n">
+        <v>23590</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Visa 8441054475956337</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Mastercard 4804370722599393</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>5239569</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>44721.59585648148</v>
+      </c>
+      <c r="D129" t="n">
+        <v>30387</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Ruble</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Visa 4756824367415661</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Discover 6499545298816238</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>5194790</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>44053.62142361111</v>
+      </c>
+      <c r="D130" t="n">
+        <v>11264</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Sol</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Mastercard 3575538110484580</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Mastercard 7236929077686727</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>2390595</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>44043.5887037037</v>
+      </c>
+      <c r="D131" t="n">
+        <v>14258</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Dollar</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Discover 5848979174601577</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Счет 24586136214737269364</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>2242467</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>44856.60421296296</v>
+      </c>
+      <c r="D132" t="n">
+        <v>18902</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Rand</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>ZAR</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Mastercard 5002772363297624</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>American Express 5688737673105581</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>4533741</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>44304.49226851852</v>
+      </c>
+      <c r="D133" t="n">
+        <v>33379</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Mastercard 5046910947182463</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>American Express 3454195292745722</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>481522</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>44699.97902777778</v>
+      </c>
+      <c r="D134" t="n">
+        <v>34210</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Krona</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Discover 0474902215594901</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>American Express 9009156961180653</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>1065726</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>44014.19873842593</v>
+      </c>
+      <c r="D135" t="n">
+        <v>29169</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Shilling</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>UGX</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Счет 02128618384427301635</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Счет 25745812541257778590</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Перевод со счета на счет</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>378251</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>44687.56908564815</v>
+      </c>
+      <c r="D136" t="n">
+        <v>32660</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Yuan Renminbi</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>American Express 3641239388125025</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Mastercard 9249013709224474</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>959523</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>44469.61811342592</v>
+      </c>
+      <c r="D137" t="n">
+        <v>22010</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Mastercard 6640372313921891</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>American Express 3669791391703828</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>3766082</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>44132.8465625</v>
+      </c>
+      <c r="D138" t="n">
+        <v>14937</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Dalasi</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>GMD</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Visa 6453536798067238</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Счет 16771823456925574978</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2504828</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>44277.24946759259</v>
+      </c>
+      <c r="D139" t="n">
+        <v>11982</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Счет 40357013384457231147</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Счет 59361600183832821416</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Перевод со счета на счет</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>1888243</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>44246.5433912037</v>
+      </c>
+      <c r="D140" t="n">
+        <v>29324</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Manat</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>TMT</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Discover 5478099584092921</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Mastercard 2255596566027326</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>4790207</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>44325.13180555555</v>
+      </c>
+      <c r="D141" t="n">
+        <v>16084</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Kwanza</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>AOA</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Visa 4625906322198608</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Счет 66619332174598187292</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Перевод организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>3373939</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>44166.91703703703</v>
+      </c>
+      <c r="D142" t="n">
+        <v>22520</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>American Express 0871573566179515</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Mastercard 7671773179035343</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2560558</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C143" s="1" t="n">
+        <v>44327.7453125</v>
+      </c>
+      <c r="D143" t="n">
+        <v>19892</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Franc</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Mastercard 7733979172661103</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Visa 9976862606592955</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>15414</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>44784.47774305556</v>
+      </c>
+      <c r="D144" t="n">
+        <v>31525</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Kuna</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>HRK</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Mastercard 5868288926724263</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>American Express 9132809122792706</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>4269608</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>45042.48612268519</v>
+      </c>
+      <c r="D145" t="n">
+        <v>33703</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Rupiah</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Счет 78769556201569913464</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>595305</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>45160.72243055556</v>
+      </c>
+      <c r="D146" t="n">
+        <v>22624</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Счет 97565556730475585217</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Открытие вклада</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>1245327</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>44264.03944444445</v>
+      </c>
+      <c r="D147" t="n">
+        <v>24252</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Somoni</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>TJS</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Discover 3233958335206913</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Visa 6269545625045856</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>

--- a/src/transactions.xlsx
+++ b/src/transactions.xlsx
@@ -469,7 +469,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2130098</v>
+        <v>5457678</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -477,29 +477,29 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>43989.46638888889</v>
+        <v>45234.44414351852</v>
       </c>
       <c r="D2" t="n">
-        <v>30731</v>
+        <v>22951</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Visa 5749750597771353</t>
+          <t>Mastercard 6219443780959412</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>American Express 9106381490184499</t>
+          <t>Visa 4786131684105875</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4653427</v>
+        <v>1999804</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -518,40 +518,40 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>44108.50859953704</v>
+        <v>45227.47049768519</v>
       </c>
       <c r="D3" t="n">
-        <v>34072</v>
+        <v>34455</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Hryvnia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>UAH</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Discover 9058011549803523</t>
+          <t>Счет 42109207415591580635</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Mastercard 5266726031439012</t>
+          <t>Счет 74058089109726743250</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод со счета на счет</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5371445</v>
+        <v>2697434</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -559,29 +559,29 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45218.16079861111</v>
+        <v>45221.42153935185</v>
       </c>
       <c r="D4" t="n">
-        <v>19556</v>
+        <v>19405</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Discover 2269057629158313</t>
+          <t>Discover 3984228285377185</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Discover 1467530652300402</t>
+          <t>Discover 2678102579384092</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -592,7 +592,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5368178</v>
+        <v>5371445</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>44019.58126157407</v>
+        <v>45218.16079861111</v>
       </c>
       <c r="D5" t="n">
-        <v>22557</v>
+        <v>19556</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -617,12 +617,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mastercard 4225154400758745</t>
+          <t>Discover 2269057629158313</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Mastercard 0556460753444710</t>
+          <t>Discover 1467530652300402</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -633,7 +633,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1068715</v>
+        <v>3518973</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -641,36 +641,40 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45141.66709490741</v>
+        <v>45210.04398148148</v>
       </c>
       <c r="D6" t="n">
-        <v>18891</v>
+        <v>19653</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Visa 0383646897791685</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Счет 04362233061130879079</t>
+          <t>American Express 9980918985573635</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2051401</v>
+        <v>4935914</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -678,29 +682,29 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>44940.58314814815</v>
+        <v>45209.10013888889</v>
       </c>
       <c r="D7" t="n">
-        <v>21616</v>
+        <v>21686</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Franc</t>
+          <t>Zloty</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Discover 8023806415405011</t>
+          <t>American Express 6113480057863136</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Discover 4330675064880873</t>
+          <t>Discover 4775142254527406</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -711,7 +715,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2377317</v>
+        <v>601829</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -719,36 +723,40 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45152.41575231482</v>
+        <v>45191.21229166666</v>
       </c>
       <c r="D8" t="n">
-        <v>23305</v>
+        <v>31130</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Koruna</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CZK</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Discover 0930552143364376</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Счет 60476196595963796362</t>
+          <t>American Express 5163534531737636</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1781876</v>
+        <v>5184881</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -756,29 +764,29 @@
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>44977.46435185185</v>
+        <v>45175.09075231481</v>
       </c>
       <c r="D9" t="n">
-        <v>24586</v>
+        <v>26661</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Franc</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>American Express 4188660988695878</t>
+          <t>Visa 9854254255741256</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>American Express 4670165143133955</t>
+          <t>Visa 1574192240031041</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -789,7 +797,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>632926</v>
+        <v>595305</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -797,40 +805,36 @@
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>44527.03204861111</v>
+        <v>45160.72243055556</v>
       </c>
       <c r="D10" t="n">
-        <v>29553</v>
+        <v>22624</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>American Express 6477627838877562</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Счет 88381741644903346269</t>
+          <t>Счет 97565556730475585217</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5055836</v>
+        <v>5379915</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -838,40 +842,36 @@
         </is>
       </c>
       <c r="C11" s="1" t="n">
-        <v>44656.14523148148</v>
+        <v>45158.12024305556</v>
       </c>
       <c r="D11" t="n">
-        <v>24796</v>
+        <v>24850</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zloty</t>
+          <t>Yen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Mastercard 3588035503290783</t>
-        </is>
-      </c>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Счет 44168961306050363869</t>
+          <t>Счет 36811391490389049691</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>282352</v>
+        <v>3188844</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -879,36 +879,40 @@
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>44191.40208333333</v>
+        <v>45153.85173611111</v>
       </c>
       <c r="D12" t="n">
-        <v>32566</v>
+        <v>23993</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Visa 7320406476027149</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Счет 87117715624747483097</t>
+          <t>American Express 4821240054296686</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3463793</v>
+        <v>2377317</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -916,40 +920,36 @@
         </is>
       </c>
       <c r="C13" s="1" t="n">
-        <v>43886.3090162037</v>
+        <v>45152.41575231482</v>
       </c>
       <c r="D13" t="n">
-        <v>17655</v>
+        <v>23305</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ruble</t>
+          <t>Koruna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Mastercard 4597611385572324</t>
-        </is>
-      </c>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Visa 0264849140954307</t>
+          <t>Счет 60476196595963796362</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5008516</v>
+        <v>5245387</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -957,29 +957,29 @@
         </is>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45107.18858796296</v>
+        <v>45149.28736111111</v>
       </c>
       <c r="D14" t="n">
-        <v>19988</v>
+        <v>25234</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Baht</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Discover 0631296518388969</t>
+          <t>American Express 8621646228906535</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Mastercard 6497034908492124</t>
+          <t>American Express 8098137039932677</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -990,7 +990,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1453305</v>
+        <v>3821850</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -998,40 +998,36 @@
         </is>
       </c>
       <c r="C15" s="1" t="n">
-        <v>43989.08885416666</v>
+        <v>45148.67325231482</v>
       </c>
       <c r="D15" t="n">
-        <v>12234</v>
+        <v>23816</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ruble</t>
+          <t>Real</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Visa 6644696207526766</t>
-        </is>
-      </c>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Mastercard 8548964838326541</t>
+          <t>Счет 82229490370109855587</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5434073</v>
+        <v>2129219</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1039,29 +1035,29 @@
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>44120.02321759259</v>
+        <v>45143.78532407407</v>
       </c>
       <c r="D16" t="n">
-        <v>33634</v>
+        <v>29187</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Discover 6079985810069539</t>
+          <t>Visa 1543704869759627</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>American Express 4187003076609282</t>
+          <t>Mastercard 7023874989167897</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1072,7 +1068,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5379915</v>
+        <v>1068715</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1080,25 +1076,25 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45158.12024305556</v>
+        <v>45141.66709490741</v>
       </c>
       <c r="D17" t="n">
-        <v>24850</v>
+        <v>18891</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yen</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Счет 36811391490389049691</t>
+          <t>Счет 04362233061130879079</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1109,7 +1105,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>368297</v>
+        <v>2467622</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1117,36 +1113,40 @@
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>44671.07193287037</v>
+        <v>45138.67976851852</v>
       </c>
       <c r="D18" t="n">
-        <v>12362</v>
+        <v>15845</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sol</t>
+          <t>Real</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PEN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>American Express 3407907218075851</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Счет 73197209028710375773</t>
+          <t>Discover 3920809225480647</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>744365</v>
+        <v>3394763</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1154,40 +1154,40 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>44684.21193287037</v>
+        <v>45117.40854166666</v>
       </c>
       <c r="D19" t="n">
-        <v>22652</v>
+        <v>31406</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dollar</t>
+          <t>Yen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Discover 8093960331401116</t>
+          <t>Discover 0769625831234066</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Mastercard 1224722159463490</t>
+          <t>Счет 89698444160396708996</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1221992</v>
+        <v>1560456</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1195,40 +1195,40 @@
         </is>
       </c>
       <c r="C20" s="1" t="n">
-        <v>44246.55940972222</v>
+        <v>45115.65166666666</v>
       </c>
       <c r="D20" t="n">
-        <v>12918</v>
+        <v>15726</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ruble</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Mastercard 9775497812609116</t>
+          <t>Visa 1576854615043358</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Discover 5944506116473459</t>
+          <t>Счет 55484214540765770320</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3518973</v>
+        <v>5008516</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1236,29 +1236,29 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45210.04398148148</v>
+        <v>45107.18858796296</v>
       </c>
       <c r="D21" t="n">
-        <v>19653</v>
+        <v>19988</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Baht</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Visa 0383646897791685</t>
+          <t>Discover 0631296518388969</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>American Express 9980918985573635</t>
+          <t>Mastercard 6497034908492124</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1269,7 +1269,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3513019</v>
+        <v>2236163</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1277,40 +1277,40 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>44806.24712962963</v>
+        <v>45106.85690972222</v>
       </c>
       <c r="D22" t="n">
-        <v>13127</v>
+        <v>19612</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Discover 3114252861244492</t>
+          <t>Счет 40742441133364006255</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Visa 4627389712448189</t>
+          <t>Счет 52562367063354770261</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод со счета на счет</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1379139</v>
+        <v>481674</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1318,40 +1318,36 @@
         </is>
       </c>
       <c r="C23" s="1" t="n">
-        <v>44705.86199074074</v>
+        <v>45104.47019675926</v>
       </c>
       <c r="D23" t="n">
-        <v>14160</v>
+        <v>24192</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Manat</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AZN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Discover 9659662475890450</t>
-        </is>
-      </c>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Discover 1864760256062832</t>
+          <t>Счет 30690764917065605785</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2611948</v>
+        <v>2258909</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1359,40 +1355,40 @@
         </is>
       </c>
       <c r="C24" s="1" t="n">
-        <v>44600.71950231482</v>
+        <v>45082.0233912037</v>
       </c>
       <c r="D24" t="n">
-        <v>15911</v>
+        <v>27030</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ruble</t>
+          <t>Rand</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Discover 6348321385395461</t>
+          <t>Счет 95883985429884067440</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Mastercard 7325946652944710</t>
+          <t>Счет 98017798502227556609</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод со счета на счет</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4924104</v>
+        <v>1380530</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1400,29 +1396,29 @@
         </is>
       </c>
       <c r="C25" s="1" t="n">
-        <v>44354.72460648148</v>
+        <v>45068.53460648148</v>
       </c>
       <c r="D25" t="n">
-        <v>13036</v>
+        <v>32118</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ariary</t>
+          <t>Dong</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Mastercard 9984189726356135</t>
+          <t>Discover 1625204231900607</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>American Express 9496683068632548</t>
+          <t>Mastercard 6547698108887955</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1433,7 +1429,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3456154</v>
+        <v>4269608</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1441,40 +1437,36 @@
         </is>
       </c>
       <c r="C26" s="1" t="n">
-        <v>44594.49076388889</v>
+        <v>45042.48612268519</v>
       </c>
       <c r="D26" t="n">
-        <v>16193</v>
+        <v>33703</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Visa 8600999617172909</t>
-        </is>
-      </c>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Visa 2844866498722428</t>
+          <t>Счет 78769556201569913464</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>599027</v>
+        <v>2151382</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1482,29 +1474,29 @@
         </is>
       </c>
       <c r="C27" s="1" t="n">
-        <v>44613.12265046296</v>
+        <v>45023.0697337963</v>
       </c>
       <c r="D27" t="n">
-        <v>12373</v>
+        <v>19607</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Baht</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>American Express 6311535048493715</t>
+          <t>Discover 1869571162526318</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Discover 6103555688511371</t>
+          <t>American Express 8377763578542307</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1515,7 +1507,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3327991</v>
+        <v>2455963</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1523,40 +1515,36 @@
         </is>
       </c>
       <c r="C28" s="1" t="n">
-        <v>43832.62287037037</v>
+        <v>45010.43490740741</v>
       </c>
       <c r="D28" t="n">
-        <v>21565</v>
+        <v>31704</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tenge</t>
+          <t>Ringgit</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KZT</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Visa 6101438539947726</t>
-        </is>
-      </c>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Mastercard 1093643052935424</t>
+          <t>Счет 47700019920719928388</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4768701</v>
+        <v>4877288</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1564,29 +1552,29 @@
         </is>
       </c>
       <c r="C29" s="1" t="n">
-        <v>44770.29969907407</v>
+        <v>45007.87980324074</v>
       </c>
       <c r="D29" t="n">
-        <v>14922</v>
+        <v>32771</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Hryvnia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>UAH</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Discover 9845271582621310</t>
+          <t>Discover 3175955318657678</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Discover 2528293109343153</t>
+          <t>American Express 9365944599565412</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1597,7 +1585,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2850514</v>
+        <v>4754778</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1605,29 +1593,29 @@
         </is>
       </c>
       <c r="C30" s="1" t="n">
-        <v>44193.74528935185</v>
+        <v>45007.80353009259</v>
       </c>
       <c r="D30" t="n">
-        <v>23686</v>
+        <v>14992</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lek</t>
+          <t>Kyat</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>MMK</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Discover 9576458861815708</t>
+          <t>Discover 9055259074920445</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Mastercard 4321975182864595</t>
+          <t>American Express 3629785004484612</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1638,7 +1626,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1279142</v>
+        <v>2449358</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1646,40 +1634,40 @@
         </is>
       </c>
       <c r="C31" s="1" t="n">
-        <v>43873.56762731481</v>
+        <v>45006.64050925926</v>
       </c>
       <c r="D31" t="n">
-        <v>16376</v>
+        <v>28671</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yen</t>
+          <t>Hryvnia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>UAH</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Mastercard 5444471272260826</t>
+          <t>Счет 09503816595143782708</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Visa 9213489075974563</t>
+          <t>Счет 88842829646860865403</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод со счета на счет</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2300960</v>
+        <v>3146089</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1687,40 +1675,40 @@
         </is>
       </c>
       <c r="C32" s="1" t="n">
-        <v>43961.88818287037</v>
+        <v>44994.32703703704</v>
       </c>
       <c r="D32" t="n">
-        <v>21170</v>
+        <v>30095</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>NIO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>American Express 2077167756122624</t>
+          <t>Mastercard 1871929909720556</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Счет 12692107571051189313</t>
+          <t>Mastercard 4747357637092907</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3015231</v>
+        <v>4136534</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1728,40 +1716,40 @@
         </is>
       </c>
       <c r="C33" s="1" t="n">
-        <v>44574.13541666666</v>
+        <v>44988.81375</v>
       </c>
       <c r="D33" t="n">
-        <v>21470</v>
+        <v>21909</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Dollar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Mastercard 9800302102501629</t>
+          <t>Mastercard 4534142823002219</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Mastercard 2405382947502377</t>
+          <t>Счет 26030281604290741032</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1380530</v>
+        <v>2835186</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1769,40 +1757,36 @@
         </is>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45068.53460648148</v>
+        <v>44983.68815972222</v>
       </c>
       <c r="D34" t="n">
-        <v>32118</v>
+        <v>32137</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dong</t>
+          <t>Dinar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Discover 1625204231900607</t>
-        </is>
-      </c>
+          <t>JOD</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Mastercard 6547698108887955</t>
+          <t>Счет 08293202872152338638</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3415187</v>
+        <v>1781876</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1810,29 +1794,29 @@
         </is>
       </c>
       <c r="C35" s="1" t="n">
-        <v>44844.04048611111</v>
+        <v>44977.46435185185</v>
       </c>
       <c r="D35" t="n">
-        <v>25180</v>
+        <v>24586</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Franc</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>American Express 0358075953034789</t>
+          <t>American Express 4188660988695878</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Visa 7020384213026064</t>
+          <t>American Express 4670165143133955</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1843,7 +1827,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4026887</v>
+        <v>1428564</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1851,29 +1835,29 @@
         </is>
       </c>
       <c r="C36" s="1" t="n">
-        <v>44518.30319444444</v>
+        <v>44972.73545138889</v>
       </c>
       <c r="D36" t="n">
-        <v>34138</v>
+        <v>14411</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Franc</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Discover 1747353075279525</t>
+          <t>Visa 6741609188063628</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Visa 3125438085014296</t>
+          <t>Discover 0163518015691189</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1884,7 +1868,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>879954</v>
+        <v>115625</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1892,40 +1876,40 @@
         </is>
       </c>
       <c r="C37" s="1" t="n">
-        <v>44612.02410879629</v>
+        <v>44969.93266203703</v>
       </c>
       <c r="D37" t="n">
-        <v>19037</v>
+        <v>17130</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>American Express 7505798122789172</t>
+          <t>Mastercard 0149845709452157</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>American Express 4033942449270190</t>
+          <t>Счет 77767569336476668437</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2352308</v>
+        <v>590436</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1933,40 +1917,36 @@
         </is>
       </c>
       <c r="C38" s="1" t="n">
-        <v>44540.1234837963</v>
+        <v>44954.2778125</v>
       </c>
       <c r="D38" t="n">
-        <v>11358</v>
+        <v>25193</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lempira</t>
+          <t>Real</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HNL</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Mastercard 9035732695110352</t>
-        </is>
-      </c>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Visa 8440267076775146</t>
+          <t>Счет 46780854004272996593</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4754778</v>
+        <v>4547801</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1974,40 +1954,36 @@
         </is>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45007.80353009259</v>
+        <v>44947.99929398148</v>
       </c>
       <c r="D39" t="n">
-        <v>14992</v>
+        <v>14109</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kyat</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MMK</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Discover 9055259074920445</t>
-        </is>
-      </c>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>American Express 3629785004484612</t>
+          <t>Счет 37292228167431639458</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1358349</v>
+        <v>2051401</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2015,36 +1991,40 @@
         </is>
       </c>
       <c r="C40" s="1" t="n">
-        <v>44109.43885416666</v>
+        <v>44940.58314814815</v>
       </c>
       <c r="D40" t="n">
-        <v>31503</v>
+        <v>21616</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ruble</t>
+          <t>Franc</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>XAF</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Discover 8023806415405011</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Счет 69086868315648596195</t>
+          <t>Discover 4330675064880873</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>379155</v>
+        <v>2848273</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2052,25 +2032,25 @@
         </is>
       </c>
       <c r="C41" s="1" t="n">
-        <v>44292.85083333333</v>
+        <v>44939.85696759259</v>
       </c>
       <c r="D41" t="n">
-        <v>23765</v>
+        <v>18871</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ruble</t>
+          <t>Tugrik</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>BYR</t>
+          <t>MNT</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Счет 47740967047235244813</t>
+          <t>Счет 13106498680479579714</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2081,7 +2061,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1718927</v>
+        <v>5170766</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2089,36 +2069,40 @@
         </is>
       </c>
       <c r="C42" s="1" t="n">
-        <v>43860.00405092593</v>
+        <v>44937.77875</v>
       </c>
       <c r="D42" t="n">
-        <v>11284</v>
+        <v>15534</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Quetzal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>GTQ</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Счет 91269211633331489581</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Счет 58661644025578523199</t>
+          <t>Счет 83962090923263746792</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод со счета на счет</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2367328</v>
+        <v>3896277</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2126,40 +2110,36 @@
         </is>
       </c>
       <c r="C43" s="1" t="n">
-        <v>44802.68231481482</v>
+        <v>44932.42857638889</v>
       </c>
       <c r="D43" t="n">
-        <v>27012</v>
+        <v>12077</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Franc</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>XOF</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Discover 1781865926439519</t>
-        </is>
-      </c>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>American Express 7807738435996717</t>
+          <t>Счет 38786697703780679258</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3896277</v>
+        <v>5229572</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2167,10 +2147,10 @@
         </is>
       </c>
       <c r="C44" s="1" t="n">
-        <v>44932.42857638889</v>
+        <v>44912.67439814815</v>
       </c>
       <c r="D44" t="n">
-        <v>12077</v>
+        <v>18347</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2182,21 +2162,25 @@
           <t>IDR</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Mastercard 7491706274351135</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Счет 38786697703780679258</t>
+          <t>Discover 7569170634837533</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>4547801</v>
+        <v>2961341</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2204,36 +2188,40 @@
         </is>
       </c>
       <c r="C45" s="1" t="n">
-        <v>44947.99929398148</v>
+        <v>44900.91804398148</v>
       </c>
       <c r="D45" t="n">
-        <v>14109</v>
+        <v>19724</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Visa 5505312713585497</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Счет 37292228167431639458</t>
+          <t>Счет 63298657753084851664</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2927678</v>
+        <v>4585117</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2241,29 +2229,29 @@
         </is>
       </c>
       <c r="C46" s="1" t="n">
-        <v>43941.36869212963</v>
+        <v>44864.05114583333</v>
       </c>
       <c r="D46" t="n">
-        <v>22584</v>
+        <v>31183</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Krona</t>
+          <t>Shekel</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>ILS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Visa 5273150871379598</t>
+          <t>American Express 1645890173600671</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Visa 2228394034527340</t>
+          <t>American Express 4738095110228336</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2274,7 +2262,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2460621</v>
+        <v>4266692</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2282,36 +2270,40 @@
         </is>
       </c>
       <c r="C47" s="1" t="n">
-        <v>44163.62784722223</v>
+        <v>44861.61912037037</v>
       </c>
       <c r="D47" t="n">
-        <v>18158</v>
+        <v>11180</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Mastercard 4407294553976321</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Счет 96408418161748634691</t>
+          <t>Счет 35208387182106672186</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1100171</v>
+        <v>2242467</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2319,36 +2311,40 @@
         </is>
       </c>
       <c r="C48" s="1" t="n">
-        <v>44210.29738425926</v>
+        <v>44856.60421296296</v>
       </c>
       <c r="D48" t="n">
-        <v>11683</v>
+        <v>18902</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leu</t>
+          <t>Rand</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MDL</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>ZAR</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Mastercard 5002772363297624</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Счет 08116016835671035018</t>
+          <t>American Express 5688737673105581</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>4935914</v>
+        <v>1274896</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2356,29 +2352,29 @@
         </is>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45209.10013888889</v>
+        <v>44850.47024305556</v>
       </c>
       <c r="D49" t="n">
-        <v>21686</v>
+        <v>19839</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Zloty</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>American Express 6113480057863136</t>
+          <t>Discover 5514977218468856</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Discover 4775142254527406</t>
+          <t>Mastercard 6902754210775301</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2389,7 +2385,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4136534</v>
+        <v>3415187</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2397,40 +2393,40 @@
         </is>
       </c>
       <c r="C50" s="1" t="n">
-        <v>44988.81375</v>
+        <v>44844.04048611111</v>
       </c>
       <c r="D50" t="n">
-        <v>21909</v>
+        <v>25180</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dollar</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Mastercard 4534142823002219</t>
+          <t>American Express 0358075953034789</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Счет 26030281604290741032</t>
+          <t>Visa 7020384213026064</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4333005</v>
+        <v>1786943</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2438,29 +2434,29 @@
         </is>
       </c>
       <c r="C51" s="1" t="n">
-        <v>43867.48361111111</v>
+        <v>44841.11903935186</v>
       </c>
       <c r="D51" t="n">
-        <v>12480</v>
+        <v>29551</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ruble</t>
+          <t>Kwacha</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Mastercard 7673263953329337</t>
+          <t>Discover 1321143733747621</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Discover 6961587092605561</t>
+          <t>American Express 8378555854465389</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2471,7 +2467,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>3530319</v>
+        <v>145602</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2479,40 +2475,36 @@
         </is>
       </c>
       <c r="C52" s="1" t="n">
-        <v>44600.78423611111</v>
+        <v>44831.81436342592</v>
       </c>
       <c r="D52" t="n">
-        <v>11294</v>
+        <v>20423</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pound</t>
+          <t>Dollar</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SYP</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Счет 64339097692172543801</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Счет 65515023539147659794</t>
+          <t>Счет 96420288541936966744</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Перевод со счета на счет</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4585117</v>
+        <v>4492444</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2520,40 +2512,40 @@
         </is>
       </c>
       <c r="C53" s="1" t="n">
-        <v>44864.05114583333</v>
+        <v>44817.11194444444</v>
       </c>
       <c r="D53" t="n">
-        <v>31183</v>
+        <v>13086</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shekel</t>
+          <t>Dollar</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ILS</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>American Express 1645890173600671</t>
+          <t>Счет 07318089075038053901</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>American Express 4738095110228336</t>
+          <t>Счет 05172516288862953128</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод со счета на счет</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2236163</v>
+        <v>3513019</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2561,40 +2553,40 @@
         </is>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45106.85690972222</v>
+        <v>44806.24712962963</v>
       </c>
       <c r="D54" t="n">
-        <v>19612</v>
+        <v>13127</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Счет 40742441133364006255</t>
+          <t>Discover 3114252861244492</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Счет 52562367063354770261</t>
+          <t>Visa 4627389712448189</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Перевод со счета на счет</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>5245387</v>
+        <v>2367328</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2602,29 +2594,29 @@
         </is>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45149.28736111111</v>
+        <v>44802.68231481482</v>
       </c>
       <c r="D55" t="n">
-        <v>25234</v>
+        <v>27012</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Franc</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>American Express 8621646228906535</t>
+          <t>Discover 1781865926439519</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>American Express 8098137039932677</t>
+          <t>American Express 7807738435996717</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2635,7 +2627,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>481674</v>
+        <v>15414</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2643,36 +2635,40 @@
         </is>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45104.47019675926</v>
+        <v>44784.47774305556</v>
       </c>
       <c r="D56" t="n">
-        <v>24192</v>
+        <v>31525</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Kuna</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>HRK</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Mastercard 5868288926724263</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Счет 30690764917065605785</t>
+          <t>American Express 9132809122792706</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>5453219</v>
+        <v>3684712</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2680,36 +2676,40 @@
         </is>
       </c>
       <c r="C57" s="1" t="n">
-        <v>44008.81377314815</v>
+        <v>44784.41809027778</v>
       </c>
       <c r="D57" t="n">
-        <v>34289</v>
+        <v>13555</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Koruna</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CZK</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>American Express 3187719566240886</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Счет 23862786914703615175</t>
+          <t>American Express 4694809375452950</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2961341</v>
+        <v>4768701</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2717,40 +2717,40 @@
         </is>
       </c>
       <c r="C58" s="1" t="n">
-        <v>44900.91804398148</v>
+        <v>44770.29969907407</v>
       </c>
       <c r="D58" t="n">
-        <v>19724</v>
+        <v>14922</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Visa 5505312713585497</t>
+          <t>Discover 9845271582621310</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Счет 63298657753084851664</t>
+          <t>Discover 2528293109343153</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>4981054</v>
+        <v>5416009</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2758,36 +2758,40 @@
         </is>
       </c>
       <c r="C59" s="1" t="n">
-        <v>44735.2599537037</v>
+        <v>44763.74369212963</v>
       </c>
       <c r="D59" t="n">
-        <v>30316</v>
+        <v>14827</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Baht</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>American Express 3294381045631862</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Счет 90489082675296745022</t>
+          <t>Счет 82941857947209957540</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>145602</v>
+        <v>2327667</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2795,36 +2799,40 @@
         </is>
       </c>
       <c r="C60" s="1" t="n">
-        <v>44831.81436342592</v>
+        <v>44758.71872685185</v>
       </c>
       <c r="D60" t="n">
-        <v>20423</v>
+        <v>31550</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dollar</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>American Express 3307640951904332</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Счет 96420288541936966744</t>
+          <t>American Express 8561768757933328</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>470092</v>
+        <v>4981054</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2832,25 +2840,25 @@
         </is>
       </c>
       <c r="C61" s="1" t="n">
-        <v>44168.62060185185</v>
+        <v>44735.2599537037</v>
       </c>
       <c r="D61" t="n">
-        <v>30922</v>
+        <v>30316</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hryvnia</t>
+          <t>Baht</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UAH</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Счет 73554102589353530426</t>
+          <t>Счет 90489082675296745022</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2861,7 +2869,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>3243213</v>
+        <v>671684</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2869,36 +2877,40 @@
         </is>
       </c>
       <c r="C62" s="1" t="n">
-        <v>44046.53327546296</v>
+        <v>44725.11576388889</v>
       </c>
       <c r="D62" t="n">
-        <v>18212</v>
+        <v>27114</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Dollar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>BSD</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Discover 9737807541197254</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Mastercard 6840667987524201</t>
+          <t>Discover 0342605798844488</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4877288</v>
+        <v>5239569</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2906,29 +2918,29 @@
         </is>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45007.87980324074</v>
+        <v>44721.59585648148</v>
       </c>
       <c r="D63" t="n">
-        <v>32771</v>
+        <v>30387</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hryvnia</t>
+          <t>Ruble</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UAH</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Discover 3175955318657678</t>
+          <t>Visa 4756824367415661</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>American Express 9365944599565412</t>
+          <t>Discover 6499545298816238</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2939,7 +2951,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>5161584</v>
+        <v>1379139</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2947,40 +2959,40 @@
         </is>
       </c>
       <c r="C64" s="1" t="n">
-        <v>44206.49123842592</v>
+        <v>44705.86199074074</v>
       </c>
       <c r="D64" t="n">
-        <v>21117</v>
+        <v>14160</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Baht</t>
+          <t>Manat</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Visa 7161243147790334</t>
+          <t>Discover 9659662475890450</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Счет 76355617883095566183</t>
+          <t>Discover 1864760256062832</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2848273</v>
+        <v>481522</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2988,36 +3000,40 @@
         </is>
       </c>
       <c r="C65" s="1" t="n">
-        <v>44939.85696759259</v>
+        <v>44699.97902777778</v>
       </c>
       <c r="D65" t="n">
-        <v>18871</v>
+        <v>34210</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tugrik</t>
+          <t>Krona</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MNT</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Discover 0474902215594901</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Счет 13106498680479579714</t>
+          <t>American Express 9009156961180653</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>3146089</v>
+        <v>378251</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3025,29 +3041,29 @@
         </is>
       </c>
       <c r="C66" s="1" t="n">
-        <v>44994.32703703704</v>
+        <v>44687.56908564815</v>
       </c>
       <c r="D66" t="n">
-        <v>30095</v>
+        <v>32660</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NIO</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Mastercard 1871929909720556</t>
+          <t>American Express 3641239388125025</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Mastercard 4747357637092907</t>
+          <t>Mastercard 9249013709224474</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3058,7 +3074,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>516388</v>
+        <v>4541322</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3066,40 +3082,40 @@
         </is>
       </c>
       <c r="C67" s="1" t="n">
-        <v>44157.70619212963</v>
+        <v>44686.24666666667</v>
       </c>
       <c r="D67" t="n">
-        <v>27921</v>
+        <v>11483</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dinar</t>
+          <t>Franc</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>JOD</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Mastercard 7201033785622479</t>
+          <t>American Express 0478677534311566</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Счет 28268105792239263134</t>
+          <t>American Express 8772778718443997</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1220204</v>
+        <v>744365</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3107,10 +3123,10 @@
         </is>
       </c>
       <c r="C68" s="1" t="n">
-        <v>44603.06378472222</v>
+        <v>44684.21193287037</v>
       </c>
       <c r="D68" t="n">
-        <v>11686</v>
+        <v>22652</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3124,12 +3140,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Mastercard 4605227118045463</t>
+          <t>Discover 8093960331401116</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>American Express 5253972174427993</t>
+          <t>Mastercard 1224722159463490</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3140,7 +3156,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>3080997</v>
+        <v>3167437</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3148,36 +3164,40 @@
         </is>
       </c>
       <c r="C69" s="1" t="n">
-        <v>43879.61677083333</v>
+        <v>44682.10469907407</v>
       </c>
       <c r="D69" t="n">
-        <v>31240</v>
+        <v>25367</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Baht</t>
+          <t>Leu</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>MDL</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Discover 6290853444919537</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Счет 49075406587701019462</t>
+          <t>American Express 3907611664671296</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>552769</v>
+        <v>368297</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3185,40 +3205,36 @@
         </is>
       </c>
       <c r="C70" s="1" t="n">
-        <v>43832.06026620371</v>
+        <v>44671.07193287037</v>
       </c>
       <c r="D70" t="n">
-        <v>26325</v>
+        <v>12362</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Krona</t>
+          <t>Sol</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Discover 5367334867736788</t>
-        </is>
-      </c>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Visa 3673180759636903</t>
+          <t>Счет 73197209028710375773</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>3394763</v>
+        <v>3205257</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3226,29 +3242,29 @@
         </is>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45117.40854166666</v>
+        <v>44662.02134259259</v>
       </c>
       <c r="D71" t="n">
-        <v>31406</v>
+        <v>11280</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Yen</t>
+          <t>Ruble</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Discover 0769625831234066</t>
+          <t>Mastercard 5612504218607911</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Счет 89698444160396708996</t>
+          <t>Счет 96692813169753520384</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3259,7 +3275,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>671684</v>
+        <v>5055836</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3267,40 +3283,40 @@
         </is>
       </c>
       <c r="C72" s="1" t="n">
-        <v>44725.11576388889</v>
+        <v>44656.14523148148</v>
       </c>
       <c r="D72" t="n">
-        <v>27114</v>
+        <v>24796</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dollar</t>
+          <t>Zloty</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BSD</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Discover 9737807541197254</t>
+          <t>Mastercard 3588035503290783</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Discover 0342605798844488</t>
+          <t>Счет 44168961306050363869</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4174847</v>
+        <v>3509357</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3308,40 +3324,40 @@
         </is>
       </c>
       <c r="C73" s="1" t="n">
-        <v>44138.6059375</v>
+        <v>44655.08723379629</v>
       </c>
       <c r="D73" t="n">
-        <v>15196</v>
+        <v>25427</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dong</t>
+          <t>Sol</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>PEN</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Mastercard 2491943868249693</t>
+          <t>Visa 0317106056412201</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Discover 7077798977965820</t>
+          <t>Счет 31080002409662710330</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3684712</v>
+        <v>4668685</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3349,29 +3365,29 @@
         </is>
       </c>
       <c r="C74" s="1" t="n">
-        <v>44784.41809027778</v>
+        <v>44644.36460648148</v>
       </c>
       <c r="D74" t="n">
-        <v>13555</v>
+        <v>34310</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>American Express 3187719566240886</t>
+          <t>Mastercard 4272685591982566</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>American Express 4694809375452950</t>
+          <t>Discover 1114381807822930</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3382,7 +3398,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3724901</v>
+        <v>3932469</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3390,29 +3406,29 @@
         </is>
       </c>
       <c r="C75" s="1" t="n">
-        <v>44345.82913194445</v>
+        <v>44621.78141203704</v>
       </c>
       <c r="D75" t="n">
-        <v>33410</v>
+        <v>21678</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>American Express 0208810830776920</t>
+          <t>Discover 0803276764821082</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Mastercard 4495966967290894</t>
+          <t>Mastercard 6602596422358257</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3423,7 +3439,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1999804</v>
+        <v>599027</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3431,40 +3447,40 @@
         </is>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45227.47049768519</v>
+        <v>44613.12265046296</v>
       </c>
       <c r="D76" t="n">
-        <v>34455</v>
+        <v>12373</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hryvnia</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UAH</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Счет 42109207415591580635</t>
+          <t>American Express 6311535048493715</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Счет 74058089109726743250</t>
+          <t>Discover 6103555688511371</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Перевод со счета на счет</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1976993</v>
+        <v>879954</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3472,40 +3488,40 @@
         </is>
       </c>
       <c r="C77" s="1" t="n">
-        <v>44476.80891203704</v>
+        <v>44612.02410879629</v>
       </c>
       <c r="D77" t="n">
-        <v>14950</v>
+        <v>19037</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pound</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SYP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Discover 5138829471442482</t>
+          <t>American Express 7505798122789172</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Счет 86520143612658802382</t>
+          <t>American Express 4033942449270190</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1560456</v>
+        <v>1220204</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3513,40 +3529,40 @@
         </is>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45115.65166666666</v>
+        <v>44603.06378472222</v>
       </c>
       <c r="D78" t="n">
-        <v>15726</v>
+        <v>11686</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Dollar</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Visa 1576854615043358</t>
+          <t>Mastercard 4605227118045463</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Счет 55484214540765770320</t>
+          <t>American Express 5253972174427993</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2432689</v>
+        <v>3530319</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3554,40 +3570,40 @@
         </is>
       </c>
       <c r="C79" s="1" t="n">
-        <v>44549.33715277778</v>
+        <v>44600.78423611111</v>
       </c>
       <c r="D79" t="n">
-        <v>16687</v>
+        <v>11294</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Pound</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SYP</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Discover 0100855364826755</t>
+          <t>Счет 64339097692172543801</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Mastercard 8643424644765562</t>
+          <t>Счет 65515023539147659794</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод со счета на счет</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4315096</v>
+        <v>2611948</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3595,29 +3611,29 @@
         </is>
       </c>
       <c r="C80" s="1" t="n">
-        <v>44282.80520833333</v>
+        <v>44600.71950231482</v>
       </c>
       <c r="D80" t="n">
-        <v>16271</v>
+        <v>15911</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Zloty</t>
+          <t>Ruble</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>American Express 3568441571958482</t>
+          <t>Discover 6348321385395461</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Discover 0688707149480292</t>
+          <t>Mastercard 7325946652944710</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3628,7 +3644,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3932469</v>
+        <v>3456154</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3636,29 +3652,29 @@
         </is>
       </c>
       <c r="C81" s="1" t="n">
-        <v>44621.78141203704</v>
+        <v>44594.49076388889</v>
       </c>
       <c r="D81" t="n">
-        <v>21678</v>
+        <v>16193</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Discover 0803276764821082</t>
+          <t>Visa 8600999617172909</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Mastercard 6602596422358257</t>
+          <t>Visa 2844866498722428</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3669,7 +3685,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>5170766</v>
+        <v>3400976</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3677,40 +3693,40 @@
         </is>
       </c>
       <c r="C82" s="1" t="n">
-        <v>44937.77875</v>
+        <v>44577.39273148148</v>
       </c>
       <c r="D82" t="n">
-        <v>15534</v>
+        <v>16702</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Quetzal</t>
+          <t>Pound</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>GTQ</t>
+          <t>SYP</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Счет 91269211633331489581</t>
+          <t>Visa 2627051318570658</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Счет 83962090923263746792</t>
+          <t>Счет 67891866687752369595</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Перевод со счета на счет</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>3081948</v>
+        <v>3015231</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3718,29 +3734,29 @@
         </is>
       </c>
       <c r="C83" s="1" t="n">
-        <v>44503.39019675926</v>
+        <v>44574.13541666666</v>
       </c>
       <c r="D83" t="n">
-        <v>26241</v>
+        <v>21470</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Visa 6774409271534698</t>
+          <t>Mastercard 9800302102501629</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Discover 6125995337388389</t>
+          <t>Mastercard 2405382947502377</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3751,7 +3767,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>3458538</v>
+        <v>2432689</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3759,29 +3775,29 @@
         </is>
       </c>
       <c r="C84" s="1" t="n">
-        <v>44496.84827546297</v>
+        <v>44549.33715277778</v>
       </c>
       <c r="D84" t="n">
-        <v>25247</v>
+        <v>16687</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Mastercard 8198255172011752</t>
+          <t>Discover 0100855364826755</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>American Express 1521610110014693</t>
+          <t>Mastercard 8643424644765562</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3792,7 +3808,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>5184881</v>
+        <v>2352308</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -3800,29 +3816,29 @@
         </is>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45175.09075231481</v>
+        <v>44540.1234837963</v>
       </c>
       <c r="D85" t="n">
-        <v>26661</v>
+        <v>11358</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Lempira</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>HNL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Visa 9854254255741256</t>
+          <t>Mastercard 9035732695110352</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Visa 1574192240031041</t>
+          <t>Visa 8440267076775146</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -3833,7 +3849,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2327667</v>
+        <v>1463688</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3841,10 +3857,10 @@
         </is>
       </c>
       <c r="C86" s="1" t="n">
-        <v>44758.71872685185</v>
+        <v>44538.59173611111</v>
       </c>
       <c r="D86" t="n">
-        <v>31550</v>
+        <v>18989</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3853,28 +3869,28 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>American Express 3307640951904332</t>
+          <t>American Express 7431983574131577</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>American Express 8561768757933328</t>
+          <t>Счет 08858102338416536409</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1595672</v>
+        <v>632926</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3882,40 +3898,40 @@
         </is>
       </c>
       <c r="C87" s="1" t="n">
-        <v>44211.27791666667</v>
+        <v>44527.03204861111</v>
       </c>
       <c r="D87" t="n">
-        <v>27346</v>
+        <v>29553</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Guilder</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ANG</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Discover 3800548259118301</t>
+          <t>American Express 6477627838877562</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>American Express 3857603686856041</t>
+          <t>Счет 88381741644903346269</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4492444</v>
+        <v>4026887</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -3923,40 +3939,40 @@
         </is>
       </c>
       <c r="C88" s="1" t="n">
-        <v>44817.11194444444</v>
+        <v>44518.30319444444</v>
       </c>
       <c r="D88" t="n">
-        <v>13086</v>
+        <v>34138</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dollar</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Счет 07318089075038053901</t>
+          <t>Discover 1747353075279525</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Счет 05172516288862953128</t>
+          <t>Visa 3125438085014296</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Перевод со счета на счет</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>590436</v>
+        <v>3081948</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -3964,36 +3980,40 @@
         </is>
       </c>
       <c r="C89" s="1" t="n">
-        <v>44954.2778125</v>
+        <v>44503.39019675926</v>
       </c>
       <c r="D89" t="n">
-        <v>25193</v>
+        <v>26241</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Real</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Visa 6774409271534698</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Счет 46780854004272996593</t>
+          <t>Discover 6125995337388389</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>5416009</v>
+        <v>3458538</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -4001,40 +4021,40 @@
         </is>
       </c>
       <c r="C90" s="1" t="n">
-        <v>44763.74369212963</v>
+        <v>44496.84827546297</v>
       </c>
       <c r="D90" t="n">
-        <v>14827</v>
+        <v>25247</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>American Express 3294381045631862</t>
+          <t>Mastercard 8198255172011752</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Счет 82941857947209957540</t>
+          <t>American Express 1521610110014693</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>3386429</v>
+        <v>1976993</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -4042,29 +4062,29 @@
         </is>
       </c>
       <c r="C91" s="1" t="n">
-        <v>44324.36054398148</v>
+        <v>44476.80891203704</v>
       </c>
       <c r="D91" t="n">
-        <v>16216</v>
+        <v>14950</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Pound</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SYP</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Discover 1256970763079173</t>
+          <t>Discover 5138829471442482</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Счет 57605402872278121538</t>
+          <t>Счет 86520143612658802382</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4075,7 +4095,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2151382</v>
+        <v>959523</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -4083,29 +4103,29 @@
         </is>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45023.0697337963</v>
+        <v>44469.61811342592</v>
       </c>
       <c r="D92" t="n">
-        <v>19607</v>
+        <v>22010</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Baht</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Discover 1869571162526318</t>
+          <t>Mastercard 6640372313921891</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>American Express 8377763578542307</t>
+          <t>American Express 3669791391703828</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4116,7 +4136,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>3636529</v>
+        <v>4565275</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -4124,29 +4144,29 @@
         </is>
       </c>
       <c r="C93" s="1" t="n">
-        <v>44309.77895833334</v>
+        <v>44367.46054398148</v>
       </c>
       <c r="D93" t="n">
-        <v>17449</v>
+        <v>19321</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Naira</t>
+          <t>Ruble</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>American Express 2245008812200631</t>
+          <t>American Express 2932525563014117</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>American Express 5496713030087267</t>
+          <t>American Express 3633642385468444</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4157,7 +4177,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>4668685</v>
+        <v>4924104</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -4165,29 +4185,29 @@
         </is>
       </c>
       <c r="C94" s="1" t="n">
-        <v>44644.36460648148</v>
+        <v>44354.72460648148</v>
       </c>
       <c r="D94" t="n">
-        <v>34310</v>
+        <v>13036</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Ariary</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Mastercard 4272685591982566</t>
+          <t>Mastercard 9984189726356135</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Discover 1114381807822930</t>
+          <t>American Express 9496683068632548</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4198,7 +4218,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1681932</v>
+        <v>3724901</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -4206,29 +4226,29 @@
         </is>
       </c>
       <c r="C95" s="1" t="n">
-        <v>44192.46844907408</v>
+        <v>44345.82913194445</v>
       </c>
       <c r="D95" t="n">
-        <v>11863</v>
+        <v>33410</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Som</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UZS</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Discover 4249648000496538</t>
+          <t>American Express 0208810830776920</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Discover 4478419247437211</t>
+          <t>Mastercard 4495966967290894</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4239,7 +4259,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1274896</v>
+        <v>2560558</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -4247,29 +4267,29 @@
         </is>
       </c>
       <c r="C96" s="1" t="n">
-        <v>44850.47024305556</v>
+        <v>44327.7453125</v>
       </c>
       <c r="D96" t="n">
-        <v>19839</v>
+        <v>19892</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Franc</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Discover 5514977218468856</t>
+          <t>Mastercard 7733979172661103</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Mastercard 6902754210775301</t>
+          <t>Visa 9976862606592955</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4280,7 +4300,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>846157</v>
+        <v>4790207</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -4288,40 +4308,40 @@
         </is>
       </c>
       <c r="C97" s="1" t="n">
-        <v>43899.1303125</v>
+        <v>44325.13180555555</v>
       </c>
       <c r="D97" t="n">
-        <v>31775</v>
+        <v>16084</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Kwanza</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>AOA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Mastercard 8838784203105980</t>
+          <t>Visa 4625906322198608</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Visa 9604746164148154</t>
+          <t>Счет 66619332174598187292</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>3701103</v>
+        <v>3386429</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -4329,40 +4349,40 @@
         </is>
       </c>
       <c r="C98" s="1" t="n">
-        <v>44069.14635416667</v>
+        <v>44324.36054398148</v>
       </c>
       <c r="D98" t="n">
-        <v>27435</v>
+        <v>16216</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Mastercard 9762476852200502</t>
+          <t>Discover 1256970763079173</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Visa 1032017250021833</t>
+          <t>Счет 57605402872278121538</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1986491</v>
+        <v>3636529</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -4370,36 +4390,40 @@
         </is>
       </c>
       <c r="C99" s="1" t="n">
-        <v>44281.11376157407</v>
+        <v>44309.77895833334</v>
       </c>
       <c r="D99" t="n">
-        <v>27106</v>
+        <v>17449</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ruble</t>
+          <t>Naira</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>BYR</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
+          <t>NGN</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>American Express 2245008812200631</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Счет 49835166076184371589</t>
+          <t>American Express 5496713030087267</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>5229572</v>
+        <v>4533741</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -4407,29 +4431,29 @@
         </is>
       </c>
       <c r="C100" s="1" t="n">
-        <v>44912.67439814815</v>
+        <v>44304.49226851852</v>
       </c>
       <c r="D100" t="n">
-        <v>18347</v>
+        <v>33379</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Mastercard 7491706274351135</t>
+          <t>Mastercard 5046910947182463</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Discover 7569170634837533</t>
+          <t>American Express 3454195292745722</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4440,7 +4464,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2812198</v>
+        <v>379155</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -4448,40 +4472,36 @@
         </is>
       </c>
       <c r="C101" s="1" t="n">
-        <v>43984.14090277778</v>
+        <v>44292.85083333333</v>
       </c>
       <c r="D101" t="n">
-        <v>31822</v>
+        <v>23765</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Ruble</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Discover 0632158083785792</t>
-        </is>
-      </c>
+          <t>BYR</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>American Express 0532003528871708</t>
+          <t>Счет 47740967047235244813</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>115625</v>
+        <v>4315096</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -4489,40 +4509,40 @@
         </is>
       </c>
       <c r="C102" s="1" t="n">
-        <v>44969.93266203703</v>
+        <v>44282.80520833333</v>
       </c>
       <c r="D102" t="n">
-        <v>17130</v>
+        <v>16271</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Zloty</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Mastercard 0149845709452157</t>
+          <t>American Express 3568441571958482</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Счет 77767569336476668437</t>
+          <t>Discover 0688707149480292</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>90523</v>
+        <v>1986491</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -4530,40 +4550,36 @@
         </is>
       </c>
       <c r="C103" s="1" t="n">
-        <v>44084.64658564814</v>
+        <v>44281.11376157407</v>
       </c>
       <c r="D103" t="n">
-        <v>32773</v>
+        <v>27106</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Ruble</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Discover 2856040699058042</t>
-        </is>
-      </c>
+          <t>BYR</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Visa 6194726895133398</t>
+          <t>Счет 49835166076184371589</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1428564</v>
+        <v>2504828</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -4571,40 +4587,40 @@
         </is>
       </c>
       <c r="C104" s="1" t="n">
-        <v>44972.73545138889</v>
+        <v>44277.24946759259</v>
       </c>
       <c r="D104" t="n">
-        <v>14411</v>
+        <v>11982</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Franc</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Visa 6741609188063628</t>
+          <t>Счет 40357013384457231147</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Discover 0163518015691189</t>
+          <t>Счет 59361600183832821416</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод со счета на счет</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2129219</v>
+        <v>1245327</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -4612,29 +4628,29 @@
         </is>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45143.78532407407</v>
+        <v>44264.03944444445</v>
       </c>
       <c r="D105" t="n">
-        <v>29187</v>
+        <v>24252</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Somoni</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>TJS</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Visa 1543704869759627</t>
+          <t>Discover 3233958335206913</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Mastercard 7023874989167897</t>
+          <t>Visa 6269545625045856</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -4645,7 +4661,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>601829</v>
+        <v>1221992</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -4653,29 +4669,29 @@
         </is>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45191.21229166666</v>
+        <v>44246.55940972222</v>
       </c>
       <c r="D106" t="n">
-        <v>31130</v>
+        <v>12918</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Ruble</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Discover 0930552143364376</t>
+          <t>Mastercard 9775497812609116</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>American Express 5163534531737636</t>
+          <t>Discover 5944506116473459</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -4686,7 +4702,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>4266692</v>
+        <v>1888243</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -4694,40 +4710,40 @@
         </is>
       </c>
       <c r="C107" s="1" t="n">
-        <v>44861.61912037037</v>
+        <v>44246.5433912037</v>
       </c>
       <c r="D107" t="n">
-        <v>11180</v>
+        <v>29324</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Manat</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TMT</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Mastercard 4407294553976321</t>
+          <t>Discover 5478099584092921</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Счет 35208387182106672186</t>
+          <t>Mastercard 2255596566027326</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>814363</v>
+        <v>1595672</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -4735,29 +4751,29 @@
         </is>
       </c>
       <c r="C108" s="1" t="n">
-        <v>43859.29630787037</v>
+        <v>44211.27791666667</v>
       </c>
       <c r="D108" t="n">
-        <v>29906</v>
+        <v>27346</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Guilder</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>ANG</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>American Express 0248447631215432</t>
+          <t>Discover 3800548259118301</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>American Express 3856315470030794</t>
+          <t>American Express 3857603686856041</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -4768,7 +4784,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>3167437</v>
+        <v>1100171</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -4776,10 +4792,10 @@
         </is>
       </c>
       <c r="C109" s="1" t="n">
-        <v>44682.10469907407</v>
+        <v>44210.29738425926</v>
       </c>
       <c r="D109" t="n">
-        <v>25367</v>
+        <v>11683</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4791,25 +4807,21 @@
           <t>MDL</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Discover 6290853444919537</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>American Express 3907611664671296</t>
+          <t>Счет 08116016835671035018</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2258909</v>
+        <v>5161584</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -4817,40 +4829,40 @@
         </is>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45082.0233912037</v>
+        <v>44206.49123842592</v>
       </c>
       <c r="D110" t="n">
-        <v>27030</v>
+        <v>21117</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Rand</t>
+          <t>Baht</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Счет 95883985429884067440</t>
+          <t>Visa 7161243147790334</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Счет 98017798502227556609</t>
+          <t>Счет 76355617883095566183</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Перевод со счета на счет</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2449358</v>
+        <v>3048608</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -4858,40 +4870,40 @@
         </is>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45006.64050925926</v>
+        <v>44199.11275462963</v>
       </c>
       <c r="D111" t="n">
-        <v>28671</v>
+        <v>25207</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hryvnia</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>UAH</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Счет 09503816595143782708</t>
+          <t>Mastercard 5983030475609063</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Счет 88842829646860865403</t>
+          <t>Discover 8166276555625267</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Перевод со счета на счет</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1463688</v>
+        <v>2850514</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -4899,40 +4911,40 @@
         </is>
       </c>
       <c r="C112" s="1" t="n">
-        <v>44538.59173611111</v>
+        <v>44193.74528935185</v>
       </c>
       <c r="D112" t="n">
-        <v>18989</v>
+        <v>23686</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Lek</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>American Express 7431983574131577</t>
+          <t>Discover 9576458861815708</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Счет 08858102338416536409</t>
+          <t>Mastercard 4321975182864595</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>3821850</v>
+        <v>1681932</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -4940,36 +4952,40 @@
         </is>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45148.67325231482</v>
+        <v>44192.46844907408</v>
       </c>
       <c r="D113" t="n">
-        <v>23816</v>
+        <v>11863</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Real</t>
+          <t>Som</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr"/>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Discover 4249648000496538</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Счет 82229490370109855587</t>
+          <t>Discover 4478419247437211</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1786943</v>
+        <v>282352</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -4977,40 +4993,36 @@
         </is>
       </c>
       <c r="C114" s="1" t="n">
-        <v>44841.11903935186</v>
+        <v>44191.40208333333</v>
       </c>
       <c r="D114" t="n">
-        <v>29551</v>
+        <v>32566</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kwacha</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ZMW</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Discover 1321143733747621</t>
-        </is>
-      </c>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>American Express 8378555854465389</t>
+          <t>Счет 87117715624747483097</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2467622</v>
+        <v>470092</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -5018,40 +5030,36 @@
         </is>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45138.67976851852</v>
+        <v>44168.62060185185</v>
       </c>
       <c r="D115" t="n">
-        <v>15845</v>
+        <v>30922</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Real</t>
+          <t>Hryvnia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>American Express 3407907218075851</t>
-        </is>
-      </c>
+          <t>UAH</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Discover 3920809225480647</t>
+          <t>Счет 73554102589353530426</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>3205257</v>
+        <v>3373939</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -5059,40 +5067,40 @@
         </is>
       </c>
       <c r="C116" s="1" t="n">
-        <v>44662.02134259259</v>
+        <v>44166.91703703703</v>
       </c>
       <c r="D116" t="n">
-        <v>11280</v>
+        <v>22520</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ruble</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Mastercard 5612504218607911</t>
+          <t>American Express 0871573566179515</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Счет 96692813169753520384</t>
+          <t>Mastercard 7671773179035343</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1932532</v>
+        <v>2460621</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -5100,40 +5108,36 @@
         </is>
       </c>
       <c r="C117" s="1" t="n">
-        <v>43880.01195601852</v>
+        <v>44163.62784722223</v>
       </c>
       <c r="D117" t="n">
-        <v>25246</v>
+        <v>18158</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Forint</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HUF</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Discover 6177546839517597</t>
-        </is>
-      </c>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>American Express 9695664158183113</t>
+          <t>Счет 96408418161748634691</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>4541322</v>
+        <v>516388</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -5141,40 +5145,40 @@
         </is>
       </c>
       <c r="C118" s="1" t="n">
-        <v>44686.24666666667</v>
+        <v>44157.70619212963</v>
       </c>
       <c r="D118" t="n">
-        <v>11483</v>
+        <v>27921</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Franc</t>
+          <t>Dinar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>JOD</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>American Express 0478677534311566</t>
+          <t>Mastercard 7201033785622479</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>American Express 8772778718443997</t>
+          <t>Счет 28268105792239263134</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>3400976</v>
+        <v>4174847</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -5182,40 +5186,40 @@
         </is>
       </c>
       <c r="C119" s="1" t="n">
-        <v>44577.39273148148</v>
+        <v>44138.6059375</v>
       </c>
       <c r="D119" t="n">
-        <v>16702</v>
+        <v>15196</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Pound</t>
+          <t>Dong</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SYP</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Visa 2627051318570658</t>
+          <t>Mastercard 2491943868249693</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Счет 67891866687752369595</t>
+          <t>Discover 7077798977965820</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>4565275</v>
+        <v>3766082</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -5223,40 +5227,40 @@
         </is>
       </c>
       <c r="C120" s="1" t="n">
-        <v>44367.46054398148</v>
+        <v>44132.8465625</v>
       </c>
       <c r="D120" t="n">
-        <v>19321</v>
+        <v>14937</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ruble</t>
+          <t>Dalasi</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>American Express 2932525563014117</t>
+          <t>Visa 6453536798067238</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>American Express 3633642385468444</t>
+          <t>Счет 16771823456925574978</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2697434</v>
+        <v>5434073</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -5264,29 +5268,29 @@
         </is>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45221.42153935185</v>
+        <v>44120.02321759259</v>
       </c>
       <c r="D121" t="n">
-        <v>19405</v>
+        <v>33634</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Discover 3984228285377185</t>
+          <t>Discover 6079985810069539</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Discover 2678102579384092</t>
+          <t>American Express 4187003076609282</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5297,7 +5301,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2455963</v>
+        <v>1358349</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -5305,25 +5309,25 @@
         </is>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45010.43490740741</v>
+        <v>44109.43885416666</v>
       </c>
       <c r="D122" t="n">
-        <v>31704</v>
+        <v>31503</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ringgit</t>
+          <t>Ruble</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MYR</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Счет 47700019920719928388</t>
+          <t>Счет 69086868315648596195</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5334,7 +5338,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2835186</v>
+        <v>4653427</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -5342,36 +5346,40 @@
         </is>
       </c>
       <c r="C123" s="1" t="n">
-        <v>44983.68815972222</v>
+        <v>44108.50859953704</v>
       </c>
       <c r="D123" t="n">
-        <v>32137</v>
+        <v>34072</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dinar</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>JOD</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Discover 9058011549803523</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Счет 08293202872152338638</t>
+          <t>Mastercard 5266726031439012</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>3509357</v>
+        <v>90523</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -5379,40 +5387,40 @@
         </is>
       </c>
       <c r="C124" s="1" t="n">
-        <v>44655.08723379629</v>
+        <v>44084.64658564814</v>
       </c>
       <c r="D124" t="n">
-        <v>25427</v>
+        <v>32773</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sol</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PEN</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Visa 0317106056412201</t>
+          <t>Discover 2856040699058042</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Счет 31080002409662710330</t>
+          <t>Visa 6194726895133398</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>5457678</v>
+        <v>3701103</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -5420,29 +5428,29 @@
         </is>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45234.44414351852</v>
+        <v>44069.14635416667</v>
       </c>
       <c r="D125" t="n">
-        <v>22951</v>
+        <v>27435</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Mastercard 6219443780959412</t>
+          <t>Mastercard 9762476852200502</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Visa 4786131684105875</t>
+          <t>Visa 1032017250021833</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -5453,7 +5461,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>3188844</v>
+        <v>5194790</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -5461,29 +5469,29 @@
         </is>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45153.85173611111</v>
+        <v>44053.62142361111</v>
       </c>
       <c r="D126" t="n">
-        <v>23993</v>
+        <v>11264</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Sol</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>PEN</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Visa 7320406476027149</t>
+          <t>Mastercard 3575538110484580</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>American Express 4821240054296686</t>
+          <t>Mastercard 7236929077686727</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -5494,7 +5502,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>3048608</v>
+        <v>3243213</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -5502,40 +5510,36 @@
         </is>
       </c>
       <c r="C127" s="1" t="n">
-        <v>44199.11275462963</v>
+        <v>44046.53327546296</v>
       </c>
       <c r="D127" t="n">
-        <v>25207</v>
+        <v>18212</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Mastercard 5983030475609063</t>
-        </is>
-      </c>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Discover 8166276555625267</t>
+          <t>Mastercard 6840667987524201</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>5270713</v>
+        <v>2390595</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -5543,40 +5547,40 @@
         </is>
       </c>
       <c r="C128" s="1" t="n">
-        <v>43996.29068287037</v>
+        <v>44043.5887037037</v>
       </c>
       <c r="D128" t="n">
-        <v>23590</v>
+        <v>14258</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Dollar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Visa 8441054475956337</t>
+          <t>Discover 5848979174601577</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Mastercard 4804370722599393</t>
+          <t>Счет 24586136214737269364</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>5239569</v>
+        <v>5368178</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -5584,29 +5588,29 @@
         </is>
       </c>
       <c r="C129" s="1" t="n">
-        <v>44721.59585648148</v>
+        <v>44019.58126157407</v>
       </c>
       <c r="D129" t="n">
-        <v>30387</v>
+        <v>22557</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ruble</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Visa 4756824367415661</t>
+          <t>Mastercard 4225154400758745</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Discover 6499545298816238</t>
+          <t>Mastercard 0556460753444710</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -5617,7 +5621,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>5194790</v>
+        <v>1065726</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -5625,40 +5629,40 @@
         </is>
       </c>
       <c r="C130" s="1" t="n">
-        <v>44053.62142361111</v>
+        <v>44014.19873842593</v>
       </c>
       <c r="D130" t="n">
-        <v>11264</v>
+        <v>29169</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sol</t>
+          <t>Shilling</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PEN</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Mastercard 3575538110484580</t>
+          <t>Счет 02128618384427301635</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Mastercard 7236929077686727</t>
+          <t>Счет 25745812541257778590</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод со счета на счет</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2390595</v>
+        <v>5453219</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -5666,40 +5670,36 @@
         </is>
       </c>
       <c r="C131" s="1" t="n">
-        <v>44043.5887037037</v>
+        <v>44008.81377314815</v>
       </c>
       <c r="D131" t="n">
-        <v>14258</v>
+        <v>34289</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dollar</t>
+          <t>Koruna</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Discover 5848979174601577</t>
-        </is>
-      </c>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Счет 24586136214737269364</t>
+          <t>Счет 23862786914703615175</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2242467</v>
+        <v>5270713</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -5707,29 +5707,29 @@
         </is>
       </c>
       <c r="C132" s="1" t="n">
-        <v>44856.60421296296</v>
+        <v>43996.29068287037</v>
       </c>
       <c r="D132" t="n">
-        <v>18902</v>
+        <v>23590</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Rand</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Mastercard 5002772363297624</t>
+          <t>Visa 8441054475956337</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>American Express 5688737673105581</t>
+          <t>Mastercard 4804370722599393</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -5740,7 +5740,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>4533741</v>
+        <v>2130098</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="C133" s="1" t="n">
-        <v>44304.49226851852</v>
+        <v>43989.46638888889</v>
       </c>
       <c r="D133" t="n">
-        <v>33379</v>
+        <v>30731</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5765,12 +5765,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Mastercard 5046910947182463</t>
+          <t>Visa 5749750597771353</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>American Express 3454195292745722</t>
+          <t>American Express 9106381490184499</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -5781,7 +5781,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>481522</v>
+        <v>1453305</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -5789,29 +5789,29 @@
         </is>
       </c>
       <c r="C134" s="1" t="n">
-        <v>44699.97902777778</v>
+        <v>43989.08885416666</v>
       </c>
       <c r="D134" t="n">
-        <v>34210</v>
+        <v>12234</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Krona</t>
+          <t>Ruble</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Discover 0474902215594901</t>
+          <t>Visa 6644696207526766</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>American Express 9009156961180653</t>
+          <t>Mastercard 8548964838326541</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -5822,7 +5822,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1065726</v>
+        <v>2812198</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -5830,40 +5830,40 @@
         </is>
       </c>
       <c r="C135" s="1" t="n">
-        <v>44014.19873842593</v>
+        <v>43984.14090277778</v>
       </c>
       <c r="D135" t="n">
-        <v>29169</v>
+        <v>31822</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shilling</t>
+          <t>Yuan Renminbi</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Счет 02128618384427301635</t>
+          <t>Discover 0632158083785792</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Счет 25745812541257778590</t>
+          <t>American Express 0532003528871708</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Перевод со счета на счет</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>378251</v>
+        <v>2300960</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -5871,40 +5871,40 @@
         </is>
       </c>
       <c r="C136" s="1" t="n">
-        <v>44687.56908564815</v>
+        <v>43961.88818287037</v>
       </c>
       <c r="D136" t="n">
-        <v>32660</v>
+        <v>21170</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Yuan Renminbi</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>American Express 3641239388125025</t>
+          <t>American Express 2077167756122624</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Mastercard 9249013709224474</t>
+          <t>Счет 12692107571051189313</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Перевод организации</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>959523</v>
+        <v>2927678</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -5912,29 +5912,29 @@
         </is>
       </c>
       <c r="C137" s="1" t="n">
-        <v>44469.61811342592</v>
+        <v>43941.36869212963</v>
       </c>
       <c r="D137" t="n">
-        <v>22010</v>
+        <v>22584</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Krona</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Mastercard 6640372313921891</t>
+          <t>Visa 5273150871379598</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>American Express 3669791391703828</t>
+          <t>Visa 2228394034527340</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -5945,7 +5945,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>3766082</v>
+        <v>846157</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -5953,40 +5953,40 @@
         </is>
       </c>
       <c r="C138" s="1" t="n">
-        <v>44132.8465625</v>
+        <v>43899.1303125</v>
       </c>
       <c r="D138" t="n">
-        <v>14937</v>
+        <v>31775</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Dalasi</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>IDR</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Visa 6453536798067238</t>
+          <t>Mastercard 8838784203105980</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Счет 16771823456925574978</t>
+          <t>Visa 9604746164148154</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2504828</v>
+        <v>3463793</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -5994,40 +5994,40 @@
         </is>
       </c>
       <c r="C139" s="1" t="n">
-        <v>44277.24946759259</v>
+        <v>43886.3090162037</v>
       </c>
       <c r="D139" t="n">
-        <v>11982</v>
+        <v>17655</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Ruble</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Счет 40357013384457231147</t>
+          <t>Mastercard 4597611385572324</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Счет 59361600183832821416</t>
+          <t>Visa 0264849140954307</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Перевод со счета на счет</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1888243</v>
+        <v>1932532</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -6035,29 +6035,29 @@
         </is>
       </c>
       <c r="C140" s="1" t="n">
-        <v>44246.5433912037</v>
+        <v>43880.01195601852</v>
       </c>
       <c r="D140" t="n">
-        <v>29324</v>
+        <v>25246</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Manat</t>
+          <t>Forint</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>TMT</t>
+          <t>HUF</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Discover 5478099584092921</t>
+          <t>Discover 6177546839517597</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Mastercard 2255596566027326</t>
+          <t>American Express 9695664158183113</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6068,7 +6068,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>4790207</v>
+        <v>3080997</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -6076,40 +6076,36 @@
         </is>
       </c>
       <c r="C141" s="1" t="n">
-        <v>44325.13180555555</v>
+        <v>43879.61677083333</v>
       </c>
       <c r="D141" t="n">
-        <v>16084</v>
+        <v>31240</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kwanza</t>
+          <t>Baht</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>AOA</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Visa 4625906322198608</t>
-        </is>
-      </c>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Счет 66619332174598187292</t>
+          <t>Счет 49075406587701019462</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Перевод организации</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>3373939</v>
+        <v>1279142</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -6117,29 +6113,29 @@
         </is>
       </c>
       <c r="C142" s="1" t="n">
-        <v>44166.91703703703</v>
+        <v>43873.56762731481</v>
       </c>
       <c r="D142" t="n">
-        <v>22520</v>
+        <v>16376</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Yen</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>IDR</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>American Express 0871573566179515</t>
+          <t>Mastercard 5444471272260826</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Mastercard 7671773179035343</t>
+          <t>Visa 9213489075974563</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6150,7 +6146,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2560558</v>
+        <v>4333005</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -6158,29 +6154,29 @@
         </is>
       </c>
       <c r="C143" s="1" t="n">
-        <v>44327.7453125</v>
+        <v>43867.48361111111</v>
       </c>
       <c r="D143" t="n">
-        <v>19892</v>
+        <v>12480</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Franc</t>
+          <t>Ruble</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Mastercard 7733979172661103</t>
+          <t>Mastercard 7673263953329337</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Visa 9976862606592955</t>
+          <t>Discover 6961587092605561</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -6191,7 +6187,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>15414</v>
+        <v>1718927</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -6199,40 +6195,36 @@
         </is>
       </c>
       <c r="C144" s="1" t="n">
-        <v>44784.47774305556</v>
+        <v>43860.00405092593</v>
       </c>
       <c r="D144" t="n">
-        <v>31525</v>
+        <v>11284</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Kuna</t>
+          <t>Rupiah</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>HRK</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Mastercard 5868288926724263</t>
-        </is>
-      </c>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>American Express 9132809122792706</t>
+          <t>Счет 58661644025578523199</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Перевод с карты на карту</t>
+          <t>Открытие вклада</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>4269608</v>
+        <v>814363</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -6240,36 +6232,40 @@
         </is>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45042.48612268519</v>
+        <v>43859.29630787037</v>
       </c>
       <c r="D145" t="n">
-        <v>33703</v>
+        <v>29906</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Rupiah</t>
+          <t>Euro</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr"/>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>American Express 0248447631215432</t>
+        </is>
+      </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Счет 78769556201569913464</t>
+          <t>American Express 3856315470030794</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>595305</v>
+        <v>3327991</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -6277,36 +6273,40 @@
         </is>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45160.72243055556</v>
+        <v>43832.62287037037</v>
       </c>
       <c r="D146" t="n">
-        <v>22624</v>
+        <v>21565</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Tenge</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr"/>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Visa 6101438539947726</t>
+        </is>
+      </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Счет 97565556730475585217</t>
+          <t>Mastercard 1093643052935424</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Открытие вклада</t>
+          <t>Перевод с карты на карту</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1245327</v>
+        <v>552769</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -6314,29 +6314,29 @@
         </is>
       </c>
       <c r="C147" s="1" t="n">
-        <v>44264.03944444445</v>
+        <v>43832.06026620371</v>
       </c>
       <c r="D147" t="n">
-        <v>24252</v>
+        <v>26325</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Somoni</t>
+          <t>Krona</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>TJS</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Discover 3233958335206913</t>
+          <t>Discover 5367334867736788</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Visa 6269545625045856</t>
+          <t>Visa 3673180759636903</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
